--- a/registration_forms/032_youth_soccer_camp_registration_form--registration_forms.xlsx
+++ b/registration_forms/032_youth_soccer_camp_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_accept_the_terms',_'value':_1}</t>
+          <t>i_accept_the_terms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I accept the terms', 'value': 1}</t>
+          <t>I accept the terms</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_do_not_accept_the_terms',_'value':_2}</t>
+          <t>i_do_not_accept_the_terms</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I do not accept the terms', 'value': 2}</t>
+          <t>I do not accept the terms</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_have_read_and_understand_the_terms',_'value':_1}</t>
+          <t>i_have_read_and_understand_the_terms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I have read and understand the terms', 'value': 1}</t>
+          <t>I have read and understand the terms</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_have_not_read_and_understand_the_terms',_'value':_2}</t>
+          <t>i_have_not_read_and_understand_the_terms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I have not read and understand the terms', 'value': 2}</t>
+          <t>I have not read and understand the terms</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male',_'value':_1}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'male', 'value': 1}</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female',_'value':_2}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'female', 'value': 2}</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_a',_'value':_1}</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team A', 'value': 1}</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_b',_'value':_2}</t>
+          <t>team_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team B', 'value': 2}</t>
+          <t>Team B</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'goalkeeper',_'value':_1}</t>
+          <t>goalkeeper</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Goalkeeper', 'value': 1}</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'defender',_'value':_2}</t>
+          <t>defender</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Defender', 'value': 2}</t>
+          <t>Defender</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'midfielder',_'value':_3}</t>
+          <t>midfielder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Midfielder', 'value': 3}</t>
+          <t>Midfielder</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>player_position_choices</t>
+          <t>player_specialty_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'midfielder',_'value':_4}</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Midfielder', 'value': 4}</t>
+          <t>soccer</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'soccer',_'value':_1}</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'soccer', 'value': 1}</t>
+          <t>basketball</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'basketball',_'value':_2}</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'basketball', 'value': 2}</t>
+          <t>tennis</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>player_specialty_choices</t>
+          <t>player_skill_level_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tennis',_'value':_3}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'tennis', 'value': 3}</t>
+          <t>beginner</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'beginner',_'value':_1}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'beginner', 'value': 1}</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'intermediate',_'value':_2}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'intermediate', 'value': 2}</t>
+          <t>advanced</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>player_skill_level_choices</t>
+          <t>player_experience_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'advanced',_'value':_3}</t>
+          <t>0-1_year</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'advanced', 'value': 3}</t>
+          <t>0-1 year</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'0-1_year',_'value':_1}</t>
+          <t>2-3_years</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '0-1 year', 'value': 1}</t>
+          <t>2-3 years</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2-3_years',_'value':_2}</t>
+          <t>more_than_3_years</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2-3 years', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>player_experience_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'more_than_3_years',_'value':_3}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'more than 3 years', 'value': 3}</t>
+          <t>more than 3 years</t>
         </is>
       </c>
     </row>
